--- a/grupos/2APV - Estadisticos 20212.xlsx
+++ b/grupos/2APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -167,15 +167,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -197,9 +197,114 @@
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
     <t>CERVANTES</t>
   </si>
   <si>
@@ -212,45 +317,18 @@
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LIBRADO</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>MARIN</t>
   </si>
   <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MOSTRANZO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -260,18 +338,6 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -284,42 +350,18 @@
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
     <t>CORONADO</t>
   </si>
   <si>
-    <t>MARIA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>OCHOA</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
@@ -329,12 +371,6 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
@@ -350,51 +386,24 @@
     <t>MARILYN</t>
   </si>
   <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
     <t>CRISTIAN FERMIN</t>
   </si>
   <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
     <t>ZABDIEL</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
     <t>IKER XAVIER</t>
   </si>
   <si>
-    <t>THANIA CRISTAL</t>
-  </si>
-  <si>
     <t>DANIEL OCTAVIO</t>
   </si>
   <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -402,15 +411,6 @@
   </si>
   <si>
     <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
   </si>
 </sst>
 </file>
@@ -921,10 +921,10 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -984,10 +984,10 @@
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -1010,10 +1010,10 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1073,10 +1073,10 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -1099,10 +1099,10 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1162,10 +1162,10 @@
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1188,10 +1188,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1251,10 +1251,10 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1277,10 +1277,10 @@
         <v>6</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1340,10 +1340,10 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1366,10 +1366,10 @@
         <v>10</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -1429,10 +1429,10 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1455,10 +1455,10 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -1518,10 +1518,10 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1544,10 +1544,10 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -1607,10 +1607,10 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1633,10 +1633,10 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -1696,10 +1696,10 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>6</v>
@@ -1722,10 +1722,10 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1785,10 +1785,10 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1811,10 +1811,10 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1874,10 +1874,10 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -2078,10 +2078,10 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>7</v>
@@ -2141,10 +2141,10 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2167,10 +2167,10 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -2230,10 +2230,10 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>6</v>
@@ -2256,10 +2256,10 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -2319,10 +2319,10 @@
         <v>9</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>6</v>
@@ -2345,10 +2345,10 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2408,10 +2408,10 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>6</v>
@@ -2434,10 +2434,10 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2497,10 +2497,10 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -2523,10 +2523,10 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2586,10 +2586,10 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2701,10 +2701,10 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2764,10 +2764,10 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2790,10 +2790,10 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>9</v>
@@ -2853,10 +2853,10 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>9</v>
@@ -2879,10 +2879,10 @@
         <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -2942,10 +2942,10 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -2968,10 +2968,10 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -3031,10 +3031,10 @@
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>6</v>
@@ -3146,10 +3146,10 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -3209,10 +3209,10 @@
         <v>8</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>6</v>
@@ -3235,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -3298,7 +3298,7 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>-1</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3372,88 +3372,94 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60.71</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>6.9</v>
+      </c>
       <c r="I2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>28</v>
       </c>
       <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G3">
+        <v>28.57</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>28</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3462,25 +3468,25 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G5">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>6.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3586,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3621,13 +3627,13 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
@@ -3635,19 +3641,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920117</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
         <v>83</v>
       </c>
-      <c r="D3" t="s">
-        <v>104</v>
-      </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>49</v>
@@ -3655,39 +3661,39 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920111</v>
+        <v>21330051920119</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920112</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
@@ -3695,99 +3701,99 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920112</v>
+        <v>21330051920391</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920113</v>
+        <v>21330051920391</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920113</v>
+        <v>21330051920122</v>
       </c>
       <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
         <v>60</v>
       </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920114</v>
+        <v>21330051920122</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920114</v>
+        <v>21330051920124</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>49</v>
@@ -3795,19 +3801,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920115</v>
+        <v>21330051920127</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
@@ -3815,59 +3821,59 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920115</v>
+        <v>21330051920128</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920116</v>
+        <v>21330051920128</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920116</v>
+        <v>21330051920128</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>49</v>
@@ -3875,19 +3881,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920117</v>
+        <v>21330051920130</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
@@ -3895,59 +3901,59 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920117</v>
+        <v>20330051920152</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920117</v>
+        <v>20330051920152</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920118</v>
+        <v>20330051920152</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>49</v>
@@ -3955,19 +3961,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920118</v>
+        <v>21330051920133</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
         <v>49</v>
@@ -3975,976 +3981,42 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920119</v>
+        <v>21330051920134</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920119</v>
+        <v>21330051920134</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920119</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920120</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920120</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920120</v>
-      </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920121</v>
-      </c>
-      <c r="B26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920121</v>
-      </c>
-      <c r="B27" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920391</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920391</v>
-      </c>
-      <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920122</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920122</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920123</v>
-      </c>
-      <c r="B32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920123</v>
-      </c>
-      <c r="B33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920124</v>
-      </c>
-      <c r="B34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920124</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920124</v>
-      </c>
-      <c r="B36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
-        <v>117</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920125</v>
-      </c>
-      <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920125</v>
-      </c>
-      <c r="B38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920126</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920126</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920127</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920127</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920127</v>
-      </c>
-      <c r="B43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D43" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920275</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920275</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920128</v>
-      </c>
-      <c r="B46" t="s">
-        <v>75</v>
-      </c>
-      <c r="C46" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" t="s">
-        <v>122</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920128</v>
-      </c>
-      <c r="B47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" t="s">
-        <v>122</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920128</v>
-      </c>
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>122</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920129</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" t="s">
-        <v>123</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920129</v>
-      </c>
-      <c r="C50" t="s">
-        <v>98</v>
-      </c>
-      <c r="D50" t="s">
-        <v>123</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920130</v>
-      </c>
-      <c r="B51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" t="s">
-        <v>124</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920130</v>
-      </c>
-      <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" t="s">
-        <v>124</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920130</v>
-      </c>
-      <c r="B53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" t="s">
-        <v>124</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920131</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" t="s">
-        <v>100</v>
-      </c>
-      <c r="D54" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920131</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>18330051920377</v>
-      </c>
-      <c r="B56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>18330051920377</v>
-      </c>
-      <c r="B57" t="s">
-        <v>78</v>
-      </c>
-      <c r="C57" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57" t="s">
-        <v>126</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920132</v>
-      </c>
-      <c r="B58" t="s">
-        <v>79</v>
-      </c>
-      <c r="C58" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920132</v>
-      </c>
-      <c r="B59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920152</v>
-      </c>
-      <c r="B60" t="s">
-        <v>80</v>
-      </c>
-      <c r="C60" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" t="s">
-        <v>128</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920152</v>
-      </c>
-      <c r="B61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" t="s">
-        <v>128</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920152</v>
-      </c>
-      <c r="B62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>128</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920133</v>
-      </c>
-      <c r="B63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" t="s">
-        <v>74</v>
-      </c>
-      <c r="D63" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920133</v>
-      </c>
-      <c r="B64" t="s">
-        <v>81</v>
-      </c>
-      <c r="C64" t="s">
-        <v>74</v>
-      </c>
-      <c r="D64" t="s">
-        <v>129</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920133</v>
-      </c>
-      <c r="B65" t="s">
-        <v>81</v>
-      </c>
-      <c r="C65" t="s">
-        <v>74</v>
-      </c>
-      <c r="D65" t="s">
-        <v>129</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920134</v>
-      </c>
-      <c r="B66" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" t="s">
-        <v>130</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920134</v>
-      </c>
-      <c r="B67" t="s">
-        <v>82</v>
-      </c>
-      <c r="C67" t="s">
-        <v>103</v>
-      </c>
-      <c r="D67" t="s">
-        <v>130</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920134</v>
-      </c>
-      <c r="B68" t="s">
-        <v>82</v>
-      </c>
-      <c r="C68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" t="s">
-        <v>130</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4980,16 +4052,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920128</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4997,16 +4069,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920117</v>
+        <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5014,308 +4086,308 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920119</v>
+        <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920122</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920124</v>
+        <v>21330051920134</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
         <v>94</v>
       </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920127</v>
+        <v>21330051920111</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920128</v>
+        <v>21330051920117</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920130</v>
+        <v>21330051920119</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920152</v>
+        <v>21330051920120</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920133</v>
+        <v>21330051920124</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920134</v>
+        <v>21330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920112</v>
+        <v>21330051920130</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920113</v>
+        <v>21330051920133</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920114</v>
+        <v>21330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920115</v>
+        <v>21330051920113</v>
       </c>
       <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
         <v>62</v>
       </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920116</v>
+        <v>21330051920114</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920118</v>
+        <v>21330051920115</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920121</v>
+        <v>21330051920116</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920391</v>
+        <v>21330051920118</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920122</v>
+        <v>21330051920121</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5323,16 +4395,16 @@
         <v>21330051920123</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5340,16 +4412,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5357,16 +4429,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5374,16 +4446,16 @@
         <v>20330051920275</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5391,13 +4463,13 @@
         <v>21330051920129</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5405,16 +4477,16 @@
         <v>21330051920131</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5422,16 +4494,16 @@
         <v>18330051920377</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5439,16 +4511,16 @@
         <v>21330051920132</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5458,7 +4530,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5490,19 +4562,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920113</v>
+        <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
@@ -5513,42 +4585,42 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920113</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920114</v>
+        <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
         <v>85</v>
       </c>
-      <c r="D4" t="s">
-        <v>107</v>
-      </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
@@ -5559,42 +4631,42 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920114</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
         <v>85</v>
       </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920116</v>
+        <v>21330051920127</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>49</v>
@@ -5605,42 +4677,42 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920116</v>
+        <v>21330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920118</v>
+        <v>21330051920130</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
@@ -5651,42 +4723,42 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920118</v>
+        <v>21330051920130</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920121</v>
+        <v>21330051920134</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>49</v>
@@ -5697,22 +4769,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920121</v>
+        <v>21330051920134</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5720,65 +4792,65 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920123</v>
+        <v>21330051920112</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920123</v>
+        <v>21330051920115</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920125</v>
+        <v>21330051920117</v>
       </c>
       <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
         <v>71</v>
       </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>49</v>
@@ -5789,19 +4861,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920125</v>
+        <v>21330051920119</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
@@ -5812,19 +4884,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920126</v>
+        <v>21330051920124</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>49</v>
@@ -5835,248 +4907,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920126</v>
+        <v>21330051920133</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>49</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920275</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920275</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920129</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920131</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920131</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>18330051920377</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>18330051920377</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920132</v>
-      </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920132</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20212.xlsx
+++ b/grupos/2APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -167,21 +167,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -194,214 +194,214 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>MONT</t>
   </si>
   <si>
-    <t>MOSTRANZO</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CAPORAL</t>
+    <t>CORONADO</t>
   </si>
   <si>
     <t>MARIA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
-    <t>PAZ</t>
+    <t>OCHOA</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
   </si>
   <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
     <t>DIANA IRAIS</t>
   </si>
   <si>
-    <t>GAEL</t>
-  </si>
-  <si>
     <t>NATALIE</t>
   </si>
   <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
   </si>
   <si>
     <t>MARCOS JESUS</t>
   </si>
   <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
     <t>PAUL ADRIAN</t>
   </si>
   <si>
-    <t>THANIA CRISTAL</t>
+    <t>IKER XAVIER</t>
+  </si>
+  <si>
+    <t>DANIEL OCTAVIO</t>
   </si>
   <si>
     <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IKER XAVIER</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
   </si>
   <si>
     <t>FATIMA</t>
@@ -915,7 +915,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -933,13 +933,13 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -948,7 +948,7 @@
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -975,13 +975,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -1022,13 +1022,13 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1037,10 +1037,10 @@
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1067,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1082,7 +1082,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1111,13 +1111,13 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1126,10 +1126,10 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1156,7 +1156,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1168,10 +1168,10 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1200,13 +1200,13 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1215,10 +1215,10 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1242,13 +1242,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1289,13 +1289,13 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1331,13 +1331,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>6</v>
@@ -1378,13 +1378,13 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1393,10 +1393,10 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1423,7 +1423,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1449,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -1467,13 +1467,13 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1482,10 +1482,10 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1509,13 +1509,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>6</v>
@@ -1527,7 +1527,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1556,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1571,10 +1571,10 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1601,7 +1601,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1613,10 +1613,10 @@
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1645,13 +1645,13 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1660,10 +1660,10 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1716,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -1734,13 +1734,13 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1749,10 +1749,10 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1776,13 +1776,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1823,13 +1823,13 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1838,10 +1838,10 @@
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1868,7 +1868,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1883,7 +1883,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1912,13 +1912,13 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1927,7 +1927,7 @@
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1954,13 +1954,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>-1</v>
@@ -1969,7 +1969,7 @@
         <v>-1</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2001,13 +2001,13 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2016,7 +2016,7 @@
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2090,13 +2090,13 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2105,10 +2105,10 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2132,10 +2132,10 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2161,7 +2161,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -2179,13 +2179,13 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2194,10 +2194,10 @@
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2221,10 +2221,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2268,13 +2268,13 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2283,7 +2283,7 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>6</v>
@@ -2357,13 +2357,13 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2405,7 +2405,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2428,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2446,13 +2446,13 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2461,10 +2461,10 @@
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2491,10 +2491,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -2535,13 +2535,13 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2550,10 +2550,10 @@
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2580,10 +2580,10 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z22">
         <v>6</v>
@@ -2624,13 +2624,13 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2639,7 +2639,7 @@
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2666,13 +2666,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>-1</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -2713,13 +2713,13 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2728,10 +2728,10 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2755,13 +2755,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>6</v>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2802,13 +2802,13 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2817,10 +2817,10 @@
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2847,7 +2847,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2891,13 +2891,13 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2906,10 +2906,10 @@
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2936,7 +2936,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2948,7 +2948,7 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>10</v>
@@ -2980,13 +2980,13 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2995,10 +2995,10 @@
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -3069,13 +3069,13 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -3084,7 +3084,7 @@
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3117,7 +3117,7 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>-1</v>
@@ -3126,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3158,13 +3158,13 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3173,7 +3173,7 @@
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3200,13 +3200,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>6</v>
@@ -3215,7 +3215,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3247,13 +3247,13 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3262,10 +3262,10 @@
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3295,7 +3295,7 @@
         <v>-1</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3304,7 +3304,7 @@
         <v>-1</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3372,30 +3372,30 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>53.57</v>
+      </c>
+      <c r="G2">
+        <v>46.43</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>60.71</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>6.9</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>39.29</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -3404,30 +3404,30 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>71.43000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="G3">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -3462,7 +3462,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3500,19 +3500,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="G6">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3532,19 +3532,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3555,28 +3555,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8">
         <v>28</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3592,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3621,159 +3621,159 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920119</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920117</v>
+        <v>21330051920391</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920119</v>
+        <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
         <v>72</v>
       </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920122</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920391</v>
+        <v>21330051920122</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920391</v>
+        <v>21330051920128</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
         <v>74</v>
       </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920122</v>
+        <v>21330051920128</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920122</v>
+        <v>21330051920128</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>51</v>
@@ -3781,59 +3781,59 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920124</v>
+        <v>20330051920152</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
         <v>75</v>
       </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920127</v>
+        <v>20330051920152</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920128</v>
+        <v>20330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>51</v>
@@ -3841,19 +3841,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920128</v>
+        <v>21330051920133</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>51</v>
@@ -3861,162 +3861,42 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920128</v>
+        <v>21330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
         <v>77</v>
       </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920130</v>
+        <v>21330051920134</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920152</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920152</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920152</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920133</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920134</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920134</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4055,13 +3935,13 @@
         <v>21330051920128</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4072,13 +3952,13 @@
         <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4089,13 +3969,13 @@
         <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4106,13 +3986,13 @@
         <v>21330051920122</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4123,13 +4003,13 @@
         <v>21330051920134</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4137,16 +4017,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920111</v>
+        <v>21330051920119</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4154,16 +4034,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920117</v>
+        <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4171,115 +4051,115 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920119</v>
+        <v>21330051920111</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920120</v>
+        <v>21330051920112</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920124</v>
+        <v>21330051920113</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920127</v>
+        <v>21330051920114</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920130</v>
+        <v>21330051920115</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920133</v>
+        <v>21330051920116</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920112</v>
+        <v>21330051920117</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>117</v>
@@ -4290,16 +4170,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920113</v>
+        <v>21330051920118</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4307,16 +4187,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920114</v>
+        <v>21330051920120</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4324,16 +4204,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920115</v>
+        <v>21330051920121</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4341,16 +4221,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920116</v>
+        <v>21330051920123</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4358,16 +4238,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920118</v>
+        <v>21330051920124</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4375,13 +4255,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920121</v>
+        <v>21330051920125</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
@@ -4392,13 +4272,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920123</v>
+        <v>21330051920126</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4409,13 +4289,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920125</v>
+        <v>21330051920127</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4426,13 +4306,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920126</v>
+        <v>20330051920275</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4443,13 +4323,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920275</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
+        <v>21330051920129</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4460,10 +4337,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920129</v>
+        <v>21330051920130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4477,10 +4357,10 @@
         <v>21330051920131</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4494,10 +4374,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4511,10 +4391,10 @@
         <v>21330051920132</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4530,7 +4410,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4562,45 +4442,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920115</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920115</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4608,22 +4488,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4631,22 +4511,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4654,45 +4534,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920127</v>
+        <v>21330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>49</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920127</v>
+        <v>21330051920112</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4700,232 +4580,117 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920130</v>
+        <v>21330051920114</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920130</v>
+        <v>21330051920119</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920134</v>
+        <v>21330051920120</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>49</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920134</v>
+        <v>21330051920127</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920112</v>
+        <v>21330051920130</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12">
         <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920117</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920119</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920124</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920133</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2APV - Estadisticos 20212.xlsx
+++ b/grupos/2APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -194,190 +194,190 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MOSTRANZO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>CAPORAL</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
   </si>
   <si>
     <t>GAEL</t>
   </si>
   <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
     <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>THANIA CRISTAL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
   </si>
   <si>
     <t>LIZBETH</t>
@@ -942,10 +942,10 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -1031,10 +1031,10 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -1073,7 +1073,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1120,10 +1120,10 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1212,7 +1212,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>6</v>
@@ -1254,7 +1254,7 @@
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1301,7 +1301,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -1343,7 +1343,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1387,10 +1387,10 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>10</v>
@@ -1479,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>6</v>
@@ -1521,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1565,10 +1565,10 @@
         <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -1610,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1627,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -1648,16 +1648,16 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>6</v>
@@ -1690,7 +1690,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1743,10 +1743,10 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -1832,10 +1832,10 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>8</v>
@@ -1900,10 +1900,10 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>6</v>
@@ -1924,13 +1924,13 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1963,10 +1963,10 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -2004,7 +2004,7 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -2099,10 +2099,10 @@
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>6</v>
@@ -2188,10 +2188,10 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>6</v>
@@ -2277,10 +2277,10 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -2319,10 +2319,10 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>6</v>
@@ -2455,10 +2455,10 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>6</v>
@@ -2500,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -2544,10 +2544,10 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2725,7 +2725,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2811,10 +2811,10 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>10</v>
@@ -2900,10 +2900,10 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>6</v>
@@ -2989,10 +2989,10 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>6</v>
@@ -3034,7 +3034,7 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>6</v>
@@ -3057,7 +3057,7 @@
         <v>7</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -3120,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>-1</v>
@@ -3167,10 +3167,10 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -3212,7 +3212,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB29">
         <v>5</v>
@@ -3238,7 +3238,7 @@
         <v>6</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>6</v>
@@ -3256,10 +3256,10 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -3301,7 +3301,7 @@
         <v>6</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>5</v>
@@ -3404,65 +3404,65 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>82.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>10.71</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>17.86</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>82.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>17.86</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -3592,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3621,39 +3621,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920119</v>
+        <v>21330051920122</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920391</v>
+        <v>21330051920122</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
@@ -3661,19 +3661,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920391</v>
+        <v>21330051920128</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>50</v>
@@ -3681,19 +3681,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920122</v>
+        <v>21330051920128</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>50</v>
@@ -3701,36 +3701,36 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920122</v>
+        <v>21330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920128</v>
+        <v>20330051920152</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3741,36 +3741,36 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920128</v>
+        <v>20330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920128</v>
+        <v>21330051920133</v>
       </c>
       <c r="B9" t="s">
         <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -3781,121 +3781,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920152</v>
+        <v>21330051920134</v>
       </c>
       <c r="B10" t="s">
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920152</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920152</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920133</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920134</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920134</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3935,13 +3835,13 @@
         <v>21330051920128</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3949,33 +3849,33 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920152</v>
+        <v>21330051920122</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920391</v>
+        <v>20330051920152</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3983,19 +3883,19 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920122</v>
+        <v>21330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4003,61 +3903,61 @@
         <v>21330051920134</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920119</v>
+        <v>21330051920111</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920133</v>
+        <v>21330051920112</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920111</v>
+        <v>21330051920113</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
@@ -4068,13 +3968,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920112</v>
+        <v>21330051920114</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
         <v>112</v>
@@ -4085,13 +3985,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920113</v>
+        <v>21330051920115</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -4102,13 +4002,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920114</v>
+        <v>21330051920116</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
         <v>114</v>
@@ -4119,13 +4019,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920115</v>
+        <v>21330051920117</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
         <v>115</v>
@@ -4136,16 +4036,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920116</v>
+        <v>21330051920118</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4153,16 +4053,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920117</v>
+        <v>21330051920119</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4170,16 +4070,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920118</v>
+        <v>21330051920120</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4187,13 +4087,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920120</v>
+        <v>21330051920121</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>118</v>
@@ -4204,13 +4104,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920121</v>
+        <v>21330051920391</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
         <v>119</v>
@@ -4224,10 +4124,10 @@
         <v>21330051920123</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -4241,10 +4141,10 @@
         <v>21330051920124</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
@@ -4258,10 +4158,10 @@
         <v>21330051920125</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
@@ -4275,10 +4175,10 @@
         <v>21330051920126</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4292,10 +4192,10 @@
         <v>21330051920127</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4309,10 +4209,10 @@
         <v>20330051920275</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4326,7 +4226,7 @@
         <v>21330051920129</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4340,10 +4240,10 @@
         <v>21330051920130</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4357,10 +4257,10 @@
         <v>21330051920131</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4374,10 +4274,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4391,10 +4291,10 @@
         <v>21330051920132</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4410,7 +4310,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4442,22 +4342,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920115</v>
+        <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4465,16 +4365,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920115</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4488,39 +4388,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920133</v>
+        <v>21330051920115</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920133</v>
+        <v>21330051920115</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4534,22 +4434,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920111</v>
+        <v>21330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4557,22 +4457,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920112</v>
+        <v>21330051920126</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4580,62 +4480,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920114</v>
+        <v>21330051920134</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920119</v>
+        <v>21330051920134</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920120</v>
+        <v>21330051920111</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4649,16 +4549,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920127</v>
+        <v>21330051920114</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4672,16 +4572,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920130</v>
+        <v>21330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4690,6 +4590,52 @@
         <v>49</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920127</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20212.xlsx
+++ b/grupos/2APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -194,10 +194,76 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MOSTRANZO</t>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>TRUJILLO</t>
@@ -209,25 +275,133 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
     <t>CLAUDIA</t>
   </si>
   <si>
-    <t>THANIA CRISTAL</t>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>IKER XAVIER</t>
+  </si>
+  <si>
+    <t>DANIEL OCTAVIO</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>GABRIELA DENISSE</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -237,180 +411,6 @@
   </si>
   <si>
     <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>IKER XAVIER</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
   </si>
 </sst>
 </file>
@@ -951,16 +951,16 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -969,16 +969,16 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -990,7 +990,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -1043,13 +1043,13 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1058,19 +1058,19 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1132,13 +1132,13 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1147,19 +1147,19 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>7</v>
@@ -1168,10 +1168,10 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1209,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -1221,13 +1221,13 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1236,16 +1236,16 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1257,7 +1257,7 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1292,13 +1292,13 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1307,16 +1307,16 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1325,16 +1325,16 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1349,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1399,13 +1399,13 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1414,10 +1414,10 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1476,7 +1476,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1488,13 +1488,13 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1503,19 +1503,19 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>6</v>
@@ -1527,7 +1527,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1577,13 +1577,13 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1592,10 +1592,10 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1616,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1666,13 +1666,13 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1681,13 +1681,13 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1702,7 +1702,7 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>7</v>
@@ -1755,13 +1755,13 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1770,16 +1770,16 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1844,13 +1844,13 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1859,16 +1859,16 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1880,7 +1880,7 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1921,7 +1921,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1933,13 +1933,13 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1948,10 +1948,10 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1960,7 +1960,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -1969,10 +1969,10 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1989,10 +1989,10 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -2010,25 +2010,25 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2037,31 +2037,31 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2111,13 +2111,13 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2126,16 +2126,16 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2147,7 +2147,7 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2200,13 +2200,13 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2215,10 +2215,10 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2227,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -2236,7 +2236,7 @@
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2271,7 +2271,7 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>6</v>
@@ -2286,16 +2286,16 @@
         <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2304,19 +2304,19 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2325,10 +2325,10 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2366,25 +2366,25 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2393,19 +2393,19 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2414,10 +2414,10 @@
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2467,13 +2467,13 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2482,13 +2482,13 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2503,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2556,13 +2556,13 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2571,16 +2571,16 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2592,7 +2592,7 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2606,13 +2606,13 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -2627,7 +2627,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2642,16 +2642,16 @@
         <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2660,22 +2660,22 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>-1</v>
@@ -2684,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2722,7 +2722,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2734,13 +2734,13 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2749,10 +2749,10 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2761,7 +2761,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>6</v>
@@ -2770,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2823,13 +2823,13 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2838,19 +2838,19 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2912,13 +2912,13 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2927,19 +2927,19 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>9</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -2948,7 +2948,7 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>10</v>
@@ -3001,13 +3001,13 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -3016,19 +3016,19 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>6</v>
@@ -3037,7 +3037,7 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC27">
         <v>9</v>
@@ -3051,7 +3051,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -3060,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -3072,31 +3072,31 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3105,16 +3105,16 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3123,7 +3123,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3140,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -3161,7 +3161,7 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -3176,16 +3176,16 @@
         <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3194,16 +3194,16 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3218,7 +3218,7 @@
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3229,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -3250,7 +3250,7 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -3268,13 +3268,13 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3283,19 +3283,19 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3304,10 +3304,10 @@
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3372,19 +3372,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>53.57</v>
+        <v>75</v>
       </c>
       <c r="G2">
-        <v>46.43</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3404,13 +3404,13 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G3">
         <v>10.71</v>
@@ -3419,10 +3419,10 @@
         <v>6.7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3436,13 +3436,13 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G4">
         <v>14.29</v>
@@ -3451,10 +3451,10 @@
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3471,27 +3471,27 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>85.70999999999999</v>
       </c>
       <c r="G5">
+        <v>14.29</v>
+      </c>
+      <c r="H5">
+        <v>6.5</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>7.3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
       <c r="J5">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3512,7 +3512,7 @@
         <v>7.14</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3523,28 +3523,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="G7">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -3592,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3621,182 +3621,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920122</v>
+        <v>21330051920128</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920122</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920128</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920128</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920128</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920152</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920152</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920133</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920134</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3835,95 +3675,95 @@
         <v>21330051920128</v>
       </c>
       <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920122</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920152</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920133</v>
+        <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920134</v>
+        <v>21330051920114</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920111</v>
+        <v>21330051920115</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
         <v>109</v>
@@ -3934,13 +3774,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920112</v>
+        <v>21330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
         <v>110</v>
@@ -3951,13 +3791,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920113</v>
+        <v>21330051920117</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
@@ -3968,16 +3808,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920114</v>
+        <v>21330051920118</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3985,16 +3825,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920115</v>
+        <v>21330051920119</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4002,16 +3842,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920116</v>
+        <v>21330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4019,16 +3859,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920117</v>
+        <v>21330051920121</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4036,16 +3876,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920118</v>
+        <v>21330051920391</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4053,13 +3893,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920119</v>
+        <v>21330051920122</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
         <v>116</v>
@@ -4070,13 +3910,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920120</v>
+        <v>21330051920123</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>117</v>
@@ -4087,13 +3927,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920121</v>
+        <v>21330051920124</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>118</v>
@@ -4104,13 +3944,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920391</v>
+        <v>21330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
         <v>119</v>
@@ -4121,13 +3961,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920123</v>
+        <v>21330051920126</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -4138,13 +3978,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920124</v>
+        <v>21330051920127</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
@@ -4155,13 +3995,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920125</v>
+        <v>20330051920275</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
@@ -4172,13 +4012,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
+        <v>21330051920129</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4189,13 +4026,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920127</v>
+        <v>21330051920130</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4206,13 +4043,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920275</v>
+        <v>21330051920131</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4223,10 +4060,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920129</v>
+        <v>18330051920377</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4237,13 +4077,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920130</v>
+        <v>21330051920132</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4254,13 +4094,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920131</v>
+        <v>20330051920152</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4271,13 +4111,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>18330051920377</v>
+        <v>21330051920133</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4288,13 +4128,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920132</v>
+        <v>21330051920134</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4310,7 +4150,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4345,13 +4185,13 @@
         <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4368,13 +4208,13 @@
         <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4388,22 +4228,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920115</v>
+        <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4411,22 +4251,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920115</v>
+        <v>21330051920391</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4437,13 +4277,13 @@
         <v>21330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4460,13 +4300,13 @@
         <v>21330051920126</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4480,39 +4320,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920134</v>
+        <v>21330051920120</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920134</v>
+        <v>21330051920125</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4526,116 +4366,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920111</v>
+        <v>21330051920134</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920114</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920120</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920127</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920130</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20212.xlsx
+++ b/grupos/2APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -170,18 +170,18 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -194,199 +194,199 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>MOSTRANZO</t>
   </si>
   <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>IKER XAVIER</t>
+  </si>
+  <si>
     <t>THANIA CRISTAL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>IKER XAVIER</t>
   </si>
   <si>
     <t>DANIEL OCTAVIO</t>
@@ -963,10 +963,10 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -1052,10 +1052,10 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1073,7 +1073,7 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1141,10 +1141,10 @@
         <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1230,10 +1230,10 @@
         <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1319,10 +1319,10 @@
         <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1408,10 +1408,10 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1497,10 +1497,10 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1586,10 +1586,10 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1607,10 +1607,10 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1675,10 +1675,10 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1696,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1764,10 +1764,10 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1853,10 +1853,10 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1874,7 +1874,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1942,10 +1942,10 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1963,10 +1963,10 @@
         <v>6</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>6</v>
@@ -2031,10 +2031,10 @@
         <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2120,10 +2120,10 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>7</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2230,7 +2230,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2298,10 +2298,10 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2319,10 +2319,10 @@
         <v>7</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2387,10 +2387,10 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -2476,10 +2476,10 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>10</v>
@@ -2565,10 +2565,10 @@
         <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -2586,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2615,7 +2615,7 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2633,10 +2633,10 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>5</v>
@@ -2654,10 +2654,10 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2675,10 +2675,10 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2743,10 +2743,10 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2832,10 +2832,10 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2921,10 +2921,10 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2942,7 +2942,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -3010,10 +3010,10 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -3031,10 +3031,10 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -3099,10 +3099,10 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -3120,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>6</v>
@@ -3188,10 +3188,10 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>5</v>
@@ -3212,7 +3212,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>5</v>
@@ -3277,10 +3277,10 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -3407,48 +3407,48 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>85.70999999999999</v>
       </c>
       <c r="G3">
-        <v>10.71</v>
+        <v>14.29</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3468,19 +3468,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="G5">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3500,19 +3500,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G6">
-        <v>7.14</v>
+        <v>3.57</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3523,28 +3523,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G7">
-        <v>7.14</v>
+        <v>3.57</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -3576,7 +3576,7 @@
         <v>3.57</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3592,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3617,26 +3617,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920128</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3672,30 +3652,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920128</v>
+        <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
         <v>105</v>
@@ -3706,13 +3686,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920112</v>
+        <v>21330051920113</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>106</v>
@@ -3723,13 +3703,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920113</v>
+        <v>21330051920114</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
         <v>107</v>
@@ -3740,13 +3720,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920114</v>
+        <v>21330051920115</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
         <v>108</v>
@@ -3757,13 +3737,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920115</v>
+        <v>21330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>109</v>
@@ -3774,13 +3754,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920116</v>
+        <v>21330051920117</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
         <v>110</v>
@@ -3791,16 +3771,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920117</v>
+        <v>21330051920118</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -3808,16 +3788,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920118</v>
+        <v>21330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3825,13 +3805,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
@@ -3842,13 +3822,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920120</v>
+        <v>21330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
@@ -3859,13 +3839,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920121</v>
+        <v>21330051920391</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
         <v>114</v>
@@ -3876,13 +3856,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920391</v>
+        <v>21330051920122</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
         <v>115</v>
@@ -3893,13 +3873,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920122</v>
+        <v>21330051920123</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
         <v>116</v>
@@ -3910,13 +3890,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920123</v>
+        <v>21330051920124</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
         <v>117</v>
@@ -3927,13 +3907,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920124</v>
+        <v>21330051920125</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
         <v>118</v>
@@ -3944,13 +3924,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
         <v>119</v>
@@ -3961,13 +3941,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920126</v>
+        <v>21330051920127</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -3978,13 +3958,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920127</v>
+        <v>20330051920275</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
@@ -3995,13 +3975,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920275</v>
+        <v>21330051920128</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
@@ -4015,7 +3995,7 @@
         <v>21330051920129</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4029,10 +4009,10 @@
         <v>21330051920130</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4046,10 +4026,10 @@
         <v>21330051920131</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4063,10 +4043,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4080,10 +4060,10 @@
         <v>21330051920132</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4097,10 +4077,10 @@
         <v>20330051920152</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4114,10 +4094,10 @@
         <v>21330051920133</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4131,10 +4111,10 @@
         <v>21330051920134</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4150,7 +4130,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4182,19 +4162,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920112</v>
+        <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>50</v>
@@ -4205,16 +4185,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920112</v>
+        <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4228,22 +4208,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920391</v>
+        <v>21330051920133</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4251,22 +4231,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920391</v>
+        <v>21330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4274,22 +4254,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920126</v>
+        <v>21330051920112</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4297,22 +4277,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920126</v>
+        <v>21330051920120</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4320,16 +4300,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920120</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4343,47 +4323,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920125</v>
+        <v>21330051920134</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920134</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
